--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -32729,7 +32729,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>324 partidos (2025-26: 306 partidos, 2026-27: 18 partidos). 28 columnas. Cargado el 12/09/2026.</t>
+          <t>324 partidos (2025-26: 306 partidos, 2026-27: 18 partidos). 28 columnas. Cargado el 13/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -32729,7 +32729,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>324 partidos (2025-26: 306 partidos, 2026-27: 18 partidos). 28 columnas. Cargado el 13/09/2026.</t>
+          <t>324 partidos (2025-26: 306 partidos, 2026-27: 18 partidos). 28 columnas. Cargado el 14/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$325</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$334</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB325"/>
+  <dimension ref="A1:AB334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -32371,8 +32371,890 @@
         <v>0</v>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I326" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J326" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K326" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L326" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M326" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N326" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O326" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P326" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q326" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="R326" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S326" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T326" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="U326" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V326" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W326" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X326" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y326" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z326" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA326" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB326" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I327" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J327" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K327" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L327" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M327" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N327" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O327" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P327" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q327" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R327" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="S327" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T327" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U327" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V327" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="W327" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="X327" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y327" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z327" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA327" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB327" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I328" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J328" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K328" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L328" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M328" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N328" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O328" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P328" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q328" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R328" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S328" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T328" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U328" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V328" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W328" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X328" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y328" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z328" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA328" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB328" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>Borussia Monchengladbach</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I329" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J329" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K329" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L329" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M329" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N329" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O329" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P329" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q329" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R329" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S329" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T329" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U329" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V329" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W329" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X329" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y329" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z329" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA329" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB329" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I330" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J330" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K330" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M330" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N330" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O330" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P330" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q330" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="R330" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S330" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T330" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U330" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V330" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W330" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X330" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y330" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB330" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I331" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K331" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L331" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M331" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N331" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O331" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P331" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q331" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R331" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S331" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T331" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U331" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V331" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W331" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X331" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z331" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB331" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I332" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J332" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K332" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L332" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M332" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N332" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O332" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P332" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q332" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R332" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="S332" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T332" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U332" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V332" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W332" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X332" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y332" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z332" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA332" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB332" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I333" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J333" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K333" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L333" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M333" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N333" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O333" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P333" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q333" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R333" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S333" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T333" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U333" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V333" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W333" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X333" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y333" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z333" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA333" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB333" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I334" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J334" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K334" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L334" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M334" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N334" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O334" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P334" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q334" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R334" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="S334" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T334" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U334" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V334" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W334" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X334" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y334" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z334" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA334" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB334" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB325"/>
+  <autoFilter ref="A1:AB334"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32729,7 +33611,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>324 partidos (2025-26: 306 partidos, 2026-27: 18 partidos). 28 columnas. Cargado el 14/09/2026.</t>
+          <t>333 partidos (2025-26: 306 partidos, 2026-27: 27 partidos). 28 columnas. Cargado el 15/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -33611,7 +33611,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>333 partidos (2025-26: 306 partidos, 2026-27: 27 partidos). 28 columnas. Cargado el 15/09/2026.</t>
+          <t>333 partidos (2025-26: 306 partidos, 2026-27: 27 partidos). 28 columnas. Cargado el 16/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -33611,7 +33611,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>333 partidos (2025-26: 306 partidos, 2026-27: 27 partidos). 28 columnas. Cargado el 16/09/2026.</t>
+          <t>333 partidos (2025-26: 306 partidos, 2026-27: 27 partidos). 28 columnas. Cargado el 18/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -33611,7 +33611,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>333 partidos (2025-26: 306 partidos, 2026-27: 27 partidos). 28 columnas. Cargado el 18/09/2026.</t>
+          <t>333 partidos (2025-26: 306 partidos, 2026-27: 27 partidos). 28 columnas. Cargado el 19/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -33611,7 +33611,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>333 partidos (2025-26: 306 partidos, 2026-27: 27 partidos). 28 columnas. Cargado el 19/09/2026.</t>
+          <t>333 partidos (2025-26: 306 partidos, 2026-27: 27 partidos). 28 columnas. Cargado el 20/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$334</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$352</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB334"/>
+  <dimension ref="A1:AB352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -33253,8 +33253,1772 @@
         <v>0</v>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I335" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J335" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K335" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L335" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M335" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N335" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O335" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P335" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q335" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="R335" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S335" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="T335" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U335" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="V335" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W335" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X335" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y335" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z335" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA335" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB335" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I336" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J336" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K336" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L336" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M336" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N336" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O336" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P336" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q336" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="R336" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="S336" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T336" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U336" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V336" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W336" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X336" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y336" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z336" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA336" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB336" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I337" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J337" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K337" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L337" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M337" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N337" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O337" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P337" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q337" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="R337" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="S337" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T337" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U337" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V337" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W337" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X337" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y337" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z337" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA337" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB337" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>Borussia Monchengladbach</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I338" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J338" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K338" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L338" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M338" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N338" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O338" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P338" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q338" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="R338" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S338" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T338" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U338" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V338" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W338" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X338" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y338" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z338" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA338" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB338" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I339" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J339" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K339" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L339" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M339" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N339" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O339" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P339" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q339" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="R339" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S339" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="T339" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U339" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V339" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W339" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X339" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y339" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z339" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA339" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB339" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I340" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J340" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K340" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L340" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M340" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N340" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O340" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P340" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q340" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="R340" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="S340" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T340" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U340" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V340" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W340" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X340" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y340" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z340" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA340" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB340" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I341" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K341" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L341" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M341" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N341" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O341" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P341" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q341" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R341" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S341" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T341" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U341" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="V341" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W341" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X341" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y341" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z341" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA341" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB341" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I342" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J342" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K342" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L342" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M342" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N342" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O342" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P342" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q342" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R342" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S342" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T342" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U342" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V342" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W342" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X342" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y342" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z342" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA342" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB342" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I343" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J343" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K343" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L343" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M343" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N343" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O343" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P343" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q343" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R343" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="S343" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T343" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U343" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V343" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W343" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="X343" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y343" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z343" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA343" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB343" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I344" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J344" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K344" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L344" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M344" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N344" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O344" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P344" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q344" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="R344" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S344" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T344" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U344" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="V344" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W344" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X344" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y344" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z344" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA344" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB344" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I345" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J345" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K345" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L345" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M345" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N345" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O345" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P345" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q345" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="R345" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="S345" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T345" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="U345" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V345" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W345" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X345" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y345" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z345" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA345" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB345" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I346" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J346" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K346" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L346" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M346" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N346" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O346" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P346" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q346" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R346" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="S346" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T346" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U346" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V346" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W346" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X346" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y346" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z346" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA346" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB346" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I347" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J347" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K347" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L347" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M347" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N347" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O347" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P347" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q347" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="R347" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S347" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T347" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U347" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V347" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W347" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X347" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y347" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z347" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA347" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB347" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I348" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J348" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K348" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L348" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M348" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N348" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O348" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P348" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q348" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R348" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="S348" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T348" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U348" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V348" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W348" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X348" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y348" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z348" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA348" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB348" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I349" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J349" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K349" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L349" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M349" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N349" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O349" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P349" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q349" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R349" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S349" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T349" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U349" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V349" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W349" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X349" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y349" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z349" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA349" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB349" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I350" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J350" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K350" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L350" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M350" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N350" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O350" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P350" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q350" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="R350" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="S350" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T350" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="U350" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V350" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W350" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="X350" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y350" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z350" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA350" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB350" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>Borussia Monchengladbach</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I351" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J351" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K351" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L351" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M351" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N351" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O351" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P351" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q351" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R351" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S351" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T351" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U351" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V351" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W351" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="X351" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y351" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z351" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA351" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB351" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I352" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J352" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K352" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L352" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M352" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N352" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O352" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P352" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q352" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="R352" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S352" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T352" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U352" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V352" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W352" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X352" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y352" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z352" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA352" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB352" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB334"/>
+  <autoFilter ref="A1:AB352"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33611,7 +35375,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>333 partidos (2025-26: 306 partidos, 2026-27: 27 partidos). 28 columnas. Cargado el 20/09/2026.</t>
+          <t>351 partidos (2025-26: 306 partidos, 2026-27: 45 partidos). 28 columnas. Cargado el 17/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -35375,7 +35375,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>351 partidos (2025-26: 306 partidos, 2026-27: 45 partidos). 28 columnas. Cargado el 17/10/2026.</t>
+          <t>351 partidos (2025-26: 306 partidos, 2026-27: 45 partidos). 28 columnas. Cargado el 18/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -35375,7 +35375,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>351 partidos (2025-26: 306 partidos, 2026-27: 45 partidos). 28 columnas. Cargado el 18/10/2026.</t>
+          <t>351 partidos (2025-26: 306 partidos, 2026-27: 45 partidos). 28 columnas. Cargado el 19/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$352</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$361</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB352"/>
+  <dimension ref="A1:AB361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -35017,8 +35017,890 @@
         <v>0</v>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I353" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J353" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K353" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L353" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M353" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N353" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O353" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P353" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q353" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R353" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S353" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T353" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U353" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V353" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W353" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="X353" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y353" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z353" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA353" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB353" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I354" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J354" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K354" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L354" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M354" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N354" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O354" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P354" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q354" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R354" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="S354" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T354" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U354" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V354" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="W354" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="X354" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y354" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z354" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA354" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB354" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I355" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J355" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K355" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L355" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M355" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N355" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O355" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P355" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q355" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R355" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="S355" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T355" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U355" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V355" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W355" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X355" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y355" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z355" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA355" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB355" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I356" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J356" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K356" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L356" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M356" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N356" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O356" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P356" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q356" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R356" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S356" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T356" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U356" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V356" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W356" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X356" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y356" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z356" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA356" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB356" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I357" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J357" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K357" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L357" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M357" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N357" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O357" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P357" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q357" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="R357" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S357" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T357" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U357" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V357" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W357" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X357" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y357" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z357" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA357" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB357" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I358" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J358" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K358" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L358" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M358" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N358" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O358" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P358" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q358" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R358" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S358" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="T358" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U358" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V358" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W358" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X358" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y358" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z358" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA358" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB358" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I359" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J359" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K359" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L359" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M359" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N359" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O359" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P359" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q359" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="R359" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S359" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="T359" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U359" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="V359" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W359" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X359" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y359" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z359" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA359" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB359" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I360" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J360" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K360" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L360" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M360" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N360" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O360" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P360" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q360" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="R360" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S360" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T360" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U360" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V360" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W360" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X360" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y360" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z360" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA360" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB360" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>Borussia Monchengladbach</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I361" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J361" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K361" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L361" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M361" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N361" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O361" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P361" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q361" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R361" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="S361" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T361" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U361" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V361" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W361" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X361" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y361" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z361" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA361" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB361" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB352"/>
+  <autoFilter ref="A1:AB361"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -35375,7 +36257,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>351 partidos (2025-26: 306 partidos, 2026-27: 45 partidos). 28 columnas. Cargado el 19/10/2026.</t>
+          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 20/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -36257,7 +36257,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 20/10/2026.</t>
+          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 21/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -36257,7 +36257,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 21/10/2026.</t>
+          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 22/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -36257,7 +36257,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 22/10/2026.</t>
+          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 21/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -36257,7 +36257,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 22/10/2026.</t>
+          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 23/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -36257,7 +36257,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 23/10/2026.</t>
+          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 24/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -36257,7 +36257,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 24/10/2026.</t>
+          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 25/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -36257,7 +36257,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 25/10/2026.</t>
+          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 26/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$361</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$370</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB361"/>
+  <dimension ref="A1:AB370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -35899,8 +35899,890 @@
         <v>0</v>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>Borussia Monchengladbach</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I362" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J362" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K362" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L362" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M362" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N362" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O362" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P362" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q362" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R362" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S362" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T362" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U362" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V362" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W362" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X362" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y362" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z362" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA362" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB362" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I363" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J363" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K363" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L363" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M363" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N363" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O363" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P363" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q363" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="R363" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S363" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T363" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U363" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V363" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W363" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X363" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y363" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z363" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA363" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB363" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q364" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R364" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S364" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T364" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U364" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V364" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W364" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="X364" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y364" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z364" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB364" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I365" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J365" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K365" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L365" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M365" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N365" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O365" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P365" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q365" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R365" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S365" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T365" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U365" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V365" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W365" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X365" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y365" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z365" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA365" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB365" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I366" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J366" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K366" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L366" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M366" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N366" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O366" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P366" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q366" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="R366" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S366" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T366" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U366" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V366" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W366" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X366" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y366" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z366" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA366" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB366" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I367" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J367" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K367" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L367" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M367" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N367" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O367" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P367" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q367" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R367" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S367" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T367" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U367" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V367" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W367" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X367" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y367" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z367" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA367" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB367" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I368" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J368" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K368" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L368" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M368" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N368" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O368" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P368" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q368" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R368" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S368" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T368" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U368" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="V368" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W368" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X368" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y368" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z368" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA368" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB368" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I369" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J369" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K369" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L369" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M369" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N369" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O369" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P369" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q369" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="R369" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S369" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T369" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U369" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V369" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W369" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X369" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y369" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z369" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA369" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB369" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I370" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J370" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K370" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L370" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M370" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N370" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O370" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P370" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q370" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="R370" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S370" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T370" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="U370" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V370" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W370" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X370" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y370" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z370" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA370" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB370" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB361"/>
+  <autoFilter ref="A1:AB370"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36257,7 +37139,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>360 partidos (2025-26: 306 partidos, 2026-27: 54 partidos). 28 columnas. Cargado el 26/10/2026.</t>
+          <t>369 partidos (2025-26: 306 partidos, 2026-27: 63 partidos). 28 columnas. Cargado el 27/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -37139,7 +37139,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>369 partidos (2025-26: 306 partidos, 2026-27: 63 partidos). 28 columnas. Cargado el 27/10/2026.</t>
+          <t>369 partidos (2025-26: 306 partidos, 2026-27: 63 partidos). 28 columnas. Cargado el 28/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -37139,7 +37139,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>369 partidos (2025-26: 306 partidos, 2026-27: 63 partidos). 28 columnas. Cargado el 28/10/2026.</t>
+          <t>369 partidos (2025-26: 306 partidos, 2026-27: 63 partidos). 28 columnas. Cargado el 29/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -37139,7 +37139,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>369 partidos (2025-26: 306 partidos, 2026-27: 63 partidos). 28 columnas. Cargado el 29/10/2026.</t>
+          <t>369 partidos (2025-26: 306 partidos, 2026-27: 63 partidos). 28 columnas. Cargado el 30/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_bundesliga.xlsx
+++ b/datos/bbdd_bundesliga.xlsx
@@ -37139,7 +37139,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>369 partidos (2025-26: 306 partidos, 2026-27: 63 partidos). 28 columnas. Cargado el 30/10/2026.</t>
+          <t>369 partidos (2025-26: 306 partidos, 2026-27: 63 partidos). 28 columnas. Cargado el 31/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
